--- a/competences2.xlsx
+++ b/competences2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trist\simple-portfolio\portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trist\Downloads\portfolio2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE083D31-1F64-42B5-B335-2B97EA8F6A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18412CFF-9797-4964-9BE9-B19776F94822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="46">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -50,14 +50,6 @@
   </si>
   <si>
     <t>Option :</t>
-  </si>
-  <si>
-    <t>▸Recenser et identifier les ressources numériques 
-▸Exploiter des référentiels, normes et standards adoptés par le prestataire informatique
-▸Mettre en place et vérifier les niveaux d’habilitation associés à un service
-▸Vérifier les conditions de la continuité d’un service informatique
-▸Gérer des sauvegardes
-▸Vérifier le respect des règles d’utilisation des ressources numériques</t>
   </si>
   <si>
     <t>▸Collecter, suivre et orienter des demandes 
@@ -116,45 +108,15 @@
     <t>▢ SISR</t>
   </si>
   <si>
-    <t>Installation et configation de serveurs Debian</t>
-  </si>
-  <si>
-    <t>Configuration de VLAN natif 999 et segmentation réseau</t>
-  </si>
-  <si>
-    <t>Déploiement d'un serveur DHCP et DNS</t>
-  </si>
-  <si>
-    <t>Supervision du réseau avec GLPI</t>
-  </si>
-  <si>
-    <t>Assistance et support aux utilisateurs</t>
-  </si>
-  <si>
     <t>Gérer le serveur</t>
   </si>
   <si>
-    <t>Installation d'OCS</t>
-  </si>
-  <si>
-    <t>Mise en place OCS</t>
-  </si>
-  <si>
-    <t>Installation de pfSense</t>
-  </si>
-  <si>
     <t>Installation du Serveur TrueNAS</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
-    <t xml:space="preserve"> X</t>
-  </si>
-  <si>
-    <t>Mise en place pfSence</t>
-  </si>
-  <si>
     <t>NOM et prénom : MOMHA Tristan</t>
   </si>
   <si>
@@ -164,7 +126,60 @@
     <t>Portfolio : https://tristanm-ort.github.io/portfolio/</t>
   </si>
   <si>
-    <t>N° candidat : 01948690879</t>
+    <t>N° candidat :  01948690879</t>
+  </si>
+  <si>
+    <t>Mise en place d’un inventaire automatisé – GLPI &amp; OCS</t>
+  </si>
+  <si>
+    <t>Configuration d’un serveur DHCP et DNS</t>
+  </si>
+  <si>
+    <t>Mise en place d’un site web sécurisé (HTTPS)</t>
+  </si>
+  <si>
+    <t>Déploiement d’un Active Directory</t>
+  </si>
+  <si>
+    <t>Mise en place d’un pare-feu PfSense</t>
+  </si>
+  <si>
+    <t>Mise en place d’un serveur de messagerie</t>
+  </si>
+  <si>
+    <t>Supervision du réseau avec Zabbix</t>
+  </si>
+  <si>
+    <t>Infrastructure réseau avec Cisco Packet Tracer</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>▸Recenser et identifier les ressources numériques 
+▸Exploiter des référentiels, normes et standards adoptés par le prestataire informatique
+▸Mettre en place et vérifier les niveaux d’habilitation associés à un xservice
+▸Vérifier les conditions de la continuité d’un service informatique
+▸Gérer des sauvegardes
+▸Vérifier le respect des règles d’utilisation des ressources numériques</t>
+  </si>
+  <si>
+    <t>Surveillance des performances et des journaux système</t>
+  </si>
+  <si>
+    <t>Mise en place et suivi des sauvegardes automatiques</t>
+  </si>
+  <si>
+    <t>Diagnostic et réparation de téléphones, tablettes et ordinateurs</t>
+  </si>
+  <si>
+    <t>Installation de logiciels et configuration d’appareils</t>
+  </si>
+  <si>
+    <t>Accueil des clients</t>
+  </si>
+  <si>
+    <t>janv-fev 2026</t>
   </si>
 </sst>
 </file>
@@ -669,7 +684,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -743,27 +758,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -779,6 +785,21 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -844,6 +865,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1164,84 +1191,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="37"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:43" ht="40.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:43" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="45"/>
+      <c r="A3" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="41"/>
+      <c r="H3" s="47"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
+      <c r="A4" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="36" t="s">
-        <v>38</v>
+      <c r="G4" s="33" t="s">
+        <v>27</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="56" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="58"/>
+      <c r="A5" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="60"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="56" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>0</v>
@@ -1263,25 +1290,25 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="47"/>
-      <c r="B7" s="55"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="57"/>
       <c r="C7" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="E7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="G7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="H7" s="9" t="s">
         <v>13</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>14</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1320,16 +1347,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="50"/>
+      <c r="A8" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1367,29 +1394,23 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="27">
+      <c r="A9" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="26">
         <v>45901</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>34</v>
-      </c>
+      <c r="C9" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="27"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="28"/>
       <c r="G9" s="23" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1429,16 +1450,22 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="27">
+        <v>31</v>
+      </c>
+      <c r="B10" s="26">
         <v>45901</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="15"/>
+      <c r="C10" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
+      <c r="G10" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="H10" s="16"/>
       <c r="I10"/>
       <c r="J10"/>
@@ -1477,30 +1504,24 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="27">
+      <c r="A11" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="26">
         <v>45901</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D11" s="15"/>
       <c r="E11" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F11" s="23"/>
       <c r="G11" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H11" s="16"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1539,29 +1560,23 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="27">
+        <v>33</v>
+      </c>
+      <c r="B12" s="26">
         <v>45901</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
       <c r="G12" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H12" s="16"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1600,29 +1615,21 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="27">
-        <v>45901</v>
+        <v>34</v>
+      </c>
+      <c r="B13" s="26">
+        <v>45962</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
       <c r="G13" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H13" s="16"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1661,29 +1668,23 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="27">
-        <v>45901</v>
+        <v>35</v>
+      </c>
+      <c r="B14" s="26">
+        <v>45992</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
       <c r="G14" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H14" s="16"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1722,13 +1723,17 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="27">
-        <v>45901</v>
-      </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="B15" s="26">
+        <v>45992</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
@@ -1771,29 +1776,23 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="27">
-        <v>45931</v>
+        <v>37</v>
+      </c>
+      <c r="B16" s="26">
+        <v>46084</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
       <c r="F16" s="15" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H16" s="16"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1831,12 +1830,8 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="27">
-        <v>45931</v>
-      </c>
+      <c r="A17" s="11"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
@@ -1925,16 +1920,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="52"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="53"/>
+      <c r="A19" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="55"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1971,30 +1966,30 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26" t="s">
-        <v>33</v>
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="25" t="s">
+        <v>24</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="H20" s="34" t="s">
-        <v>34</v>
+        <v>21</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="31" t="s">
+        <v>25</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -2034,28 +2029,28 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="H21" s="34" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="31" t="s">
+        <v>25</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -2094,14 +2089,26 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="15"/>
+      <c r="A22" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
+      <c r="F22" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="G22" s="15"/>
-      <c r="H22" s="16"/>
+      <c r="H22" s="16" t="s">
+        <v>38</v>
+      </c>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2139,14 +2146,26 @@
       <c r="AQ22"/>
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="15"/>
+      <c r="A23" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
+      <c r="F23" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
+      <c r="H23" s="16" t="s">
+        <v>38</v>
+      </c>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2319,16 +2338,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="53"/>
+      <c r="A27" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="54"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="55"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2366,13 +2385,23 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="11"/>
-      <c r="B28" s="10"/>
+      <c r="A28" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="62" t="s">
+        <v>45</v>
+      </c>
       <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
+      <c r="D28" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
+      <c r="G28" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="H28" s="16"/>
       <c r="I28"/>
       <c r="J28"/>
@@ -2411,13 +2440,23 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="10"/>
+      <c r="A29" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
+      <c r="D29" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
+      <c r="G29" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="H29" s="16"/>
       <c r="I29"/>
       <c r="J29"/>
@@ -2456,13 +2495,23 @@
       <c r="AQ29"/>
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
-      <c r="B30" s="10"/>
+      <c r="A30" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
+      <c r="D30" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
+      <c r="G30" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="H30" s="16"/>
       <c r="I30"/>
       <c r="J30"/>

--- a/competences2.xlsx
+++ b/competences2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trist\Downloads\portfolio2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trist\portfolio-final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18412CFF-9797-4964-9BE9-B19776F94822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5600A9AD-3FBF-4562-BF8C-AB77F1EFF6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1548" yWindow="2712" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -123,9 +123,6 @@
     <t>SISR</t>
   </si>
   <si>
-    <t>Portfolio : https://tristanm-ort.github.io/portfolio/</t>
-  </si>
-  <si>
     <t>N° candidat :  01948690879</t>
   </si>
   <si>
@@ -180,6 +177,9 @@
   </si>
   <si>
     <t>janv-fev 2026</t>
+  </si>
+  <si>
+    <t>Portfolio : https://tristanm-ort.github.io/portfolio-final/</t>
   </si>
 </sst>
 </file>
@@ -800,9 +800,54 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -826,51 +871,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1191,56 +1191,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="39"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:43" ht="40.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:43" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="41"/>
-      <c r="H3" s="47"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="56"/>
+      <c r="H3" s="62"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="60"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
@@ -1252,22 +1252,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="60"/>
+      <c r="A5" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="54"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="50" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1290,10 +1290,10 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="49"/>
-      <c r="B7" s="57"/>
+      <c r="A7" s="42"/>
+      <c r="B7" s="51"/>
       <c r="C7" s="20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>9</v>
@@ -1347,16 +1347,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1395,22 +1395,22 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="26">
         <v>45901</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="15"/>
       <c r="F9" s="28"/>
       <c r="G9" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1450,21 +1450,21 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="26">
         <v>45901</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H10" s="16"/>
       <c r="I10"/>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="26">
         <v>45901</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="26">
         <v>45901</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="26">
         <v>45962</v>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="26">
         <v>45992</v>
@@ -1723,16 +1723,16 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="26">
         <v>45992</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
@@ -1776,7 +1776,7 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" s="26">
         <v>46084</v>
@@ -1920,16 +1920,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="55"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="49"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2090,24 +2090,24 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -2147,24 +2147,24 @@
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
@@ -2338,16 +2338,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="53" t="s">
+      <c r="A27" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="54"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="55"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="49"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2385,22 +2385,22 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="61" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="62" t="s">
-        <v>45</v>
+      <c r="A28" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="40" t="s">
+        <v>44</v>
       </c>
       <c r="C28" s="15"/>
       <c r="D28" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H28" s="16"/>
       <c r="I28"/>
@@ -2440,22 +2440,22 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="61" t="s">
-        <v>43</v>
+      <c r="A29" s="39" t="s">
+        <v>42</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" s="15"/>
       <c r="D29" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H29" s="16"/>
       <c r="I29"/>
@@ -2495,22 +2495,22 @@
       <c r="AQ29"/>
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="61" t="s">
+      <c r="A30" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>45</v>
       </c>
       <c r="C30" s="15"/>
       <c r="D30" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H30" s="16"/>
       <c r="I30"/>
@@ -2822,6 +2822,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2829,11 +2834,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
